--- a/public/air-request-template_GW.xlsx
+++ b/public/air-request-template_GW.xlsx
@@ -1695,16 +1695,16 @@
     <mergeCell ref="R1:AC1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 AA2 W2 R3:R1048576 V3:V1048576 Z3:Z1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R1048576 V3:V1048576 Z3:Z1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT("MASTER_CLAIM[CLAIM]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT("MASTER_BRAND[BRAND_NAME]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C3:C1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>INDIRECT("MASTER_BU[BU]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>INDIRECT("MASTER_GARMENT_TYPE[DESCRIPTION]")</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M1048576" xr:uid="{00000000-0002-0000-0000-000008000000}">
